--- a/assets/images/OWASP_VMG_PSc_C_example.xlsx
+++ b/assets/images/OWASP_VMG_PSc_C_example.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elbel/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elbel/Downloads/OWASP 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0437A96-91BA-BE4E-8EC2-238DBA41B87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A84E28-8AB2-E049-B9C6-8A0644309158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="660" windowWidth="27640" windowHeight="16680" xr2:uid="{77943962-F861-B544-A54B-E941A02850D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Weekly Rolling Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,34 +50,16 @@
     <t>S4 Score</t>
   </si>
   <si>
-    <t>S4 KEV</t>
-  </si>
-  <si>
-    <t>S4 Vulns</t>
-  </si>
-  <si>
     <t>S3 C</t>
   </si>
   <si>
     <t>S3 Score</t>
   </si>
   <si>
-    <t>S3 KEV</t>
-  </si>
-  <si>
-    <t>S3 Vulns</t>
-  </si>
-  <si>
     <t>S2 C</t>
   </si>
   <si>
     <t>S2 Score</t>
-  </si>
-  <si>
-    <t>S2 KEV</t>
-  </si>
-  <si>
-    <t>S2 Vulns</t>
   </si>
   <si>
     <t>S1 C</t>
@@ -89,13 +71,31 @@
     <t>Total Hosts</t>
   </si>
   <si>
-    <t>S1 KEV</t>
+    <t>Week</t>
   </si>
   <si>
-    <t>S1 Vulns</t>
+    <t>S1 Total Xploit</t>
   </si>
   <si>
-    <t>Week</t>
+    <t>S1 Total Vulns</t>
+  </si>
+  <si>
+    <t>S2 Total Vulns</t>
+  </si>
+  <si>
+    <t>S2 Total Xploit</t>
+  </si>
+  <si>
+    <t>S3 Total Vulns</t>
+  </si>
+  <si>
+    <t>S3 Total Xploit</t>
+  </si>
+  <si>
+    <t>S4 Total Vulns</t>
+  </si>
+  <si>
+    <t>S4  Total Xploit</t>
   </si>
 </sst>
 </file>
@@ -186,13 +186,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -209,10 +209,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -523,59 +519,59 @@
     <col min="19" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="35" customHeight="1">
+    <row r="1" spans="1:18" s="7" customFormat="1" ht="35" customHeight="1">
       <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="R1" s="7" t="s">
+      <c r="Q1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -837,7 +833,7 @@
         <v>30.1584</v>
       </c>
       <c r="F6" s="2">
-        <f>SLOPE(E2:E6,A2:A6)</f>
+        <f t="shared" ref="F6:F24" si="4">SLOPE(E2:E6,A2:A6)</f>
         <v>2.0185599999999999</v>
       </c>
       <c r="G6" s="4">
@@ -851,7 +847,7 @@
         <v>10.052</v>
       </c>
       <c r="J6" s="2">
-        <f>SLOPE(I2:I6,A2:A6)</f>
+        <f t="shared" ref="J6:J24" si="5">SLOPE(I2:I6,A2:A6)</f>
         <v>1.91008</v>
       </c>
       <c r="K6" s="4">
@@ -865,7 +861,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="N6" s="4">
-        <f>SLOPE(M2:M6,A2:A6)</f>
+        <f t="shared" ref="N6:N24" si="6">SLOPE(M2:M6,A2:A6)</f>
         <v>2.0119999999999996</v>
       </c>
       <c r="O6" s="4">
@@ -879,7 +875,7 @@
         <v>10.02</v>
       </c>
       <c r="R6" s="4">
-        <f>SLOPE(Q2:Q6,A2:A6)</f>
+        <f t="shared" ref="R6:R24" si="7">SLOPE(Q2:Q6,A2:A6)</f>
         <v>1.90384</v>
       </c>
     </row>
@@ -901,7 +897,7 @@
         <v>30.1584</v>
       </c>
       <c r="F7" s="2">
-        <f>SLOPE(E3:E7,A3:A7)</f>
+        <f t="shared" si="4"/>
         <v>3.0278400000000003</v>
       </c>
       <c r="G7" s="4">
@@ -915,7 +911,7 @@
         <v>10.052</v>
       </c>
       <c r="J7" s="2">
-        <f>SLOPE(I3:I7,A3:A7)</f>
+        <f t="shared" si="5"/>
         <v>2.8651200000000001</v>
       </c>
       <c r="K7" s="4">
@@ -929,7 +925,7 @@
         <v>10.02</v>
       </c>
       <c r="N7" s="4">
-        <f>SLOPE(M3:M7,A3:A7)</f>
+        <f t="shared" si="6"/>
         <v>1.0059999999999998</v>
       </c>
       <c r="O7" s="4">
@@ -943,7 +939,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R7" s="4">
-        <f>SLOPE(Q3:Q7,A3:A7)</f>
+        <f t="shared" si="7"/>
         <v>0.95191999999999999</v>
       </c>
     </row>
@@ -965,7 +961,7 @@
         <v>30.147600000000001</v>
       </c>
       <c r="F8" s="2">
-        <f>SLOPE(E4:E8,A4:A8)</f>
+        <f t="shared" si="4"/>
         <v>3.0256800000000004</v>
       </c>
       <c r="G8" s="4">
@@ -979,7 +975,7 @@
         <v>10.052</v>
       </c>
       <c r="J8" s="2">
-        <f>SLOPE(I4:I8,A4:A8)</f>
+        <f t="shared" si="5"/>
         <v>2.8651200000000001</v>
       </c>
       <c r="K8" s="4">
@@ -993,7 +989,7 @@
         <v>10.02</v>
       </c>
       <c r="N8" s="4">
-        <f>SLOPE(M4:M8,A4:A8)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O8" s="4">
@@ -1007,7 +1003,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R8" s="4">
-        <f>SLOPE(Q4:Q8,A4:A8)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1029,7 +1025,7 @@
         <v>30.147600000000001</v>
       </c>
       <c r="F9" s="2">
-        <f>SLOPE(E5:E9,A5:A9)</f>
+        <f t="shared" si="4"/>
         <v>2.01532</v>
       </c>
       <c r="G9" s="4">
@@ -1043,7 +1039,7 @@
         <v>0.50239999999999996</v>
       </c>
       <c r="J9" s="2">
-        <f>SLOPE(I5:I9,A5:A9)</f>
+        <f t="shared" si="5"/>
         <v>1.5999999999998237E-4</v>
       </c>
       <c r="K9" s="4">
@@ -1057,7 +1053,7 @@
         <v>10.02</v>
       </c>
       <c r="N9" s="4">
-        <f>SLOPE(M5:M9,A5:A9)</f>
+        <f t="shared" si="6"/>
         <v>-1.0059999999999998</v>
       </c>
       <c r="O9" s="4">
@@ -1071,7 +1067,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R9" s="4">
-        <f>SLOPE(Q5:Q9,A5:A9)</f>
+        <f t="shared" si="7"/>
         <v>-0.95191999999999999</v>
       </c>
     </row>
@@ -1093,7 +1089,7 @@
         <v>40.276800000000001</v>
       </c>
       <c r="F10" s="2">
-        <f>SLOPE(E6:E10,A6:A10)</f>
+        <f t="shared" si="4"/>
         <v>2.0226000000000002</v>
       </c>
       <c r="G10" s="4">
@@ -1107,7 +1103,7 @@
         <v>10.068</v>
       </c>
       <c r="J10" s="2">
-        <f>SLOPE(I6:I10,A6:A10)</f>
+        <f t="shared" si="5"/>
         <v>-0.95175999999999994</v>
       </c>
       <c r="K10" s="4">
@@ -1121,7 +1117,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="N10" s="4">
-        <f>SLOPE(M6:M10,A6:A10)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O10" s="4">
@@ -1135,7 +1131,7 @@
         <v>10.02</v>
       </c>
       <c r="R10" s="4">
-        <f>SLOPE(Q6:Q10,A6:A10)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1157,7 +1153,7 @@
         <v>40.276800000000001</v>
       </c>
       <c r="F11" s="2">
-        <f>SLOPE(E7:E11,A7:A11)</f>
+        <f t="shared" si="4"/>
         <v>3.0366000000000004</v>
       </c>
       <c r="G11" s="4">
@@ -1171,7 +1167,7 @@
         <v>10.068</v>
       </c>
       <c r="J11" s="2">
-        <f>SLOPE(I7:I11,A7:A11)</f>
+        <f t="shared" si="5"/>
         <v>4.8000000000000039E-3</v>
       </c>
       <c r="K11" s="4">
@@ -1185,7 +1181,7 @@
         <v>10.02</v>
       </c>
       <c r="N11" s="4">
-        <f>SLOPE(M7:M11,A7:A11)</f>
+        <f t="shared" si="6"/>
         <v>1.0059999999999998</v>
       </c>
       <c r="O11" s="4">
@@ -1199,7 +1195,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R11" s="4">
-        <f>SLOPE(Q7:Q11,A7:A11)</f>
+        <f t="shared" si="7"/>
         <v>0.95191999999999999</v>
       </c>
     </row>
@@ -1221,7 +1217,7 @@
         <v>40.2624</v>
       </c>
       <c r="F12" s="2">
-        <f>SLOPE(E8:E12,A8:A12)</f>
+        <f t="shared" si="4"/>
         <v>3.0358799999999997</v>
       </c>
       <c r="G12" s="4">
@@ -1235,7 +1231,7 @@
         <v>10.068</v>
       </c>
       <c r="J12" s="2">
-        <f>SLOPE(I8:I12,A8:A12)</f>
+        <f t="shared" si="5"/>
         <v>0.95975999999999995</v>
       </c>
       <c r="K12" s="4">
@@ -1249,7 +1245,7 @@
         <v>10.02</v>
       </c>
       <c r="N12" s="4">
-        <f>SLOPE(M8:M12,A8:A12)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O12" s="4">
@@ -1263,7 +1259,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R12" s="4">
-        <f>SLOPE(Q8:Q12,A8:A12)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1285,7 +1281,7 @@
         <v>40.2624</v>
       </c>
       <c r="F13" s="2">
-        <f>SLOPE(E9:E13,A9:A13)</f>
+        <f t="shared" si="4"/>
         <v>2.0215199999999998</v>
       </c>
       <c r="G13" s="4">
@@ -1299,7 +1295,7 @@
         <v>0.50319999999999998</v>
       </c>
       <c r="J13" s="2">
-        <f>SLOPE(I9:I13,A9:A13)</f>
+        <f t="shared" si="5"/>
         <v>1.5999999999998237E-4</v>
       </c>
       <c r="K13" s="4">
@@ -1313,7 +1309,7 @@
         <v>10.02</v>
       </c>
       <c r="N13" s="4">
-        <f>SLOPE(M9:M13,A9:A13)</f>
+        <f t="shared" si="6"/>
         <v>-1.0059999999999998</v>
       </c>
       <c r="O13" s="4">
@@ -1327,7 +1323,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R13" s="4">
-        <f>SLOPE(Q9:Q13,A9:A13)</f>
+        <f t="shared" si="7"/>
         <v>-0.95191999999999999</v>
       </c>
     </row>
@@ -1349,7 +1345,7 @@
         <v>50.427999999999997</v>
       </c>
       <c r="F14" s="2">
-        <f>SLOPE(E10:E14,A10:A14)</f>
+        <f t="shared" si="4"/>
         <v>2.028799999999999</v>
       </c>
       <c r="G14" s="4">
@@ -1363,7 +1359,7 @@
         <v>10.084</v>
       </c>
       <c r="J14" s="2">
-        <f>SLOPE(I10:I14,A10:A14)</f>
+        <f t="shared" si="5"/>
         <v>-0.95328000000000002</v>
       </c>
       <c r="K14" s="4">
@@ -1377,7 +1373,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="N14" s="4">
-        <f>SLOPE(M10:M14,A10:A14)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O14" s="4">
@@ -1391,7 +1387,7 @@
         <v>10.02</v>
       </c>
       <c r="R14" s="4">
-        <f>SLOPE(Q10:Q14,A10:A14)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1413,7 +1409,7 @@
         <v>50.427999999999997</v>
       </c>
       <c r="F15" s="2">
-        <f>SLOPE(E11:E15,A11:A15)</f>
+        <f t="shared" si="4"/>
         <v>3.0467999999999988</v>
       </c>
       <c r="G15" s="4">
@@ -1427,7 +1423,7 @@
         <v>10.084</v>
       </c>
       <c r="J15" s="2">
-        <f>SLOPE(I11:I15,A11:A15)</f>
+        <f t="shared" si="5"/>
         <v>4.8000000000000039E-3</v>
       </c>
       <c r="K15" s="4">
@@ -1441,7 +1437,7 @@
         <v>10.02</v>
       </c>
       <c r="N15" s="4">
-        <f>SLOPE(M11:M15,A11:A15)</f>
+        <f t="shared" si="6"/>
         <v>1.0059999999999998</v>
       </c>
       <c r="O15" s="4">
@@ -1455,7 +1451,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R15" s="4">
-        <f>SLOPE(Q11:Q15,A11:A15)</f>
+        <f t="shared" si="7"/>
         <v>0.95191999999999999</v>
       </c>
     </row>
@@ -1477,7 +1473,7 @@
         <v>50.41</v>
       </c>
       <c r="F16" s="2">
-        <f>SLOPE(E12:E16,A12:A16)</f>
+        <f t="shared" si="4"/>
         <v>3.046079999999999</v>
       </c>
       <c r="G16" s="4">
@@ -1491,7 +1487,7 @@
         <v>10.084</v>
       </c>
       <c r="J16" s="2">
-        <f>SLOPE(I12:I16,A12:A16)</f>
+        <f t="shared" si="5"/>
         <v>0.96128000000000002</v>
       </c>
       <c r="K16" s="4">
@@ -1505,7 +1501,7 @@
         <v>10.02</v>
       </c>
       <c r="N16" s="4">
-        <f>SLOPE(M12:M16,A12:A16)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O16" s="4">
@@ -1519,7 +1515,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R16" s="4">
-        <f>SLOPE(Q12:Q16,A12:A16)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1541,7 +1537,7 @@
         <v>50.41</v>
       </c>
       <c r="F17" s="2">
-        <f>SLOPE(E13:E17,A13:A17)</f>
+        <f t="shared" si="4"/>
         <v>2.0277199999999995</v>
       </c>
       <c r="G17" s="4">
@@ -1555,7 +1551,7 @@
         <v>0.504</v>
       </c>
       <c r="J17" s="2">
-        <f>SLOPE(I13:I17,A13:A17)</f>
+        <f t="shared" si="5"/>
         <v>1.5999999999998237E-4</v>
       </c>
       <c r="K17" s="4">
@@ -1569,7 +1565,7 @@
         <v>10.02</v>
       </c>
       <c r="N17" s="4">
-        <f>SLOPE(M13:M17,A13:A17)</f>
+        <f t="shared" si="6"/>
         <v>-1.0059999999999998</v>
       </c>
       <c r="O17" s="4">
@@ -1583,7 +1579,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R17" s="4">
-        <f>SLOPE(Q13:Q17,A13:A17)</f>
+        <f t="shared" si="7"/>
         <v>-0.95191999999999999</v>
       </c>
     </row>
@@ -1605,7 +1601,7 @@
         <v>60.612000000000002</v>
       </c>
       <c r="F18" s="2">
-        <f>SLOPE(E14:E18,A14:A18)</f>
+        <f t="shared" si="4"/>
         <v>2.035000000000001</v>
       </c>
       <c r="G18" s="4">
@@ -1619,7 +1615,7 @@
         <v>10.1</v>
       </c>
       <c r="J18" s="2">
-        <f>SLOPE(I14:I18,A14:A18)</f>
+        <f t="shared" si="5"/>
         <v>-0.95479999999999998</v>
       </c>
       <c r="K18" s="4">
@@ -1633,7 +1629,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="N18" s="4">
-        <f>SLOPE(M14:M18,A14:A18)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O18" s="4">
@@ -1647,7 +1643,7 @@
         <v>10.02</v>
       </c>
       <c r="R18" s="4">
-        <f>SLOPE(Q14:Q18,A14:A18)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1669,7 +1665,7 @@
         <v>60.612000000000002</v>
       </c>
       <c r="F19" s="2">
-        <f>SLOPE(E15:E19,A15:A19)</f>
+        <f t="shared" si="4"/>
         <v>3.0570000000000013</v>
       </c>
       <c r="G19" s="4">
@@ -1683,7 +1679,7 @@
         <v>10.1</v>
       </c>
       <c r="J19" s="2">
-        <f>SLOPE(I15:I19,A15:A19)</f>
+        <f t="shared" si="5"/>
         <v>4.8000000000000039E-3</v>
       </c>
       <c r="K19" s="4">
@@ -1697,7 +1693,7 @@
         <v>10.02</v>
       </c>
       <c r="N19" s="4">
-        <f>SLOPE(M15:M19,A15:A19)</f>
+        <f t="shared" si="6"/>
         <v>1.0059999999999998</v>
       </c>
       <c r="O19" s="4">
@@ -1711,7 +1707,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R19" s="4">
-        <f>SLOPE(Q15:Q19,A15:A19)</f>
+        <f t="shared" si="7"/>
         <v>0.95191999999999999</v>
       </c>
     </row>
@@ -1733,7 +1729,7 @@
         <v>60.590400000000002</v>
       </c>
       <c r="F20" s="2">
-        <f>SLOPE(E16:E20,A16:A20)</f>
+        <f t="shared" si="4"/>
         <v>3.0562800000000019</v>
       </c>
       <c r="G20" s="4">
@@ -1747,7 +1743,7 @@
         <v>10.1</v>
       </c>
       <c r="J20" s="2">
-        <f>SLOPE(I16:I20,A16:A20)</f>
+        <f t="shared" si="5"/>
         <v>0.96279999999999999</v>
       </c>
       <c r="K20" s="4">
@@ -1761,7 +1757,7 @@
         <v>10.02</v>
       </c>
       <c r="N20" s="4">
-        <f>SLOPE(M16:M20,A16:A20)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O20" s="4">
@@ -1775,7 +1771,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R20" s="4">
-        <f>SLOPE(Q16:Q20,A16:A20)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1797,7 +1793,7 @@
         <v>60.590400000000002</v>
       </c>
       <c r="F21" s="2">
-        <f>SLOPE(E17:E21,A17:A21)</f>
+        <f t="shared" si="4"/>
         <v>2.0339200000000011</v>
       </c>
       <c r="G21" s="4">
@@ -1811,7 +1807,7 @@
         <v>0.50480000000000003</v>
       </c>
       <c r="J21" s="2">
-        <f>SLOPE(I17:I21,A17:A21)</f>
+        <f t="shared" si="5"/>
         <v>1.6000000000016001E-4</v>
       </c>
       <c r="K21" s="4">
@@ -1825,7 +1821,7 @@
         <v>10.02</v>
       </c>
       <c r="N21" s="4">
-        <f>SLOPE(M17:M21,A17:A21)</f>
+        <f t="shared" si="6"/>
         <v>-1.0059999999999998</v>
       </c>
       <c r="O21" s="4">
@@ -1839,7 +1835,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R21" s="4">
-        <f>SLOPE(Q17:Q21,A17:A21)</f>
+        <f t="shared" si="7"/>
         <v>-0.95191999999999999</v>
       </c>
     </row>
@@ -1861,7 +1857,7 @@
         <v>70.828800000000001</v>
       </c>
       <c r="F22" s="2">
-        <f>SLOPE(E18:E22,A18:A22)</f>
+        <f t="shared" si="4"/>
         <v>2.0411999999999999</v>
       </c>
       <c r="G22" s="4">
@@ -1875,7 +1871,7 @@
         <v>10.116</v>
       </c>
       <c r="J22" s="2">
-        <f>SLOPE(I18:I22,A18:A22)</f>
+        <f t="shared" si="5"/>
         <v>-0.95631999999999984</v>
       </c>
       <c r="K22" s="4">
@@ -1889,7 +1885,7 @@
         <v>20.079999999999998</v>
       </c>
       <c r="N22" s="4">
-        <f>SLOPE(M18:M22,A18:A22)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O22" s="4">
@@ -1903,7 +1899,7 @@
         <v>10.02</v>
       </c>
       <c r="R22" s="4">
-        <f>SLOPE(Q18:Q22,A18:A22)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1925,7 +1921,7 @@
         <v>70.828800000000001</v>
       </c>
       <c r="F23" s="2">
-        <f>SLOPE(E19:E23,A19:A23)</f>
+        <f t="shared" si="4"/>
         <v>3.0671999999999997</v>
       </c>
       <c r="G23" s="4">
@@ -1939,7 +1935,7 @@
         <v>10.116</v>
       </c>
       <c r="J23" s="2">
-        <f>SLOPE(I19:I23,A19:A23)</f>
+        <f t="shared" si="5"/>
         <v>4.8000000000000039E-3</v>
       </c>
       <c r="K23" s="4">
@@ -1953,7 +1949,7 @@
         <v>10.02</v>
       </c>
       <c r="N23" s="4">
-        <f>SLOPE(M19:M23,A19:A23)</f>
+        <f t="shared" si="6"/>
         <v>1.0059999999999998</v>
       </c>
       <c r="O23" s="4">
@@ -1967,7 +1963,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R23" s="4">
-        <f>SLOPE(Q19:Q23,A19:A23)</f>
+        <f t="shared" si="7"/>
         <v>0.95191999999999999</v>
       </c>
     </row>
@@ -1989,7 +1985,7 @@
         <v>70.803600000000003</v>
       </c>
       <c r="F24" s="2">
-        <f>SLOPE(E20:E24,A20:A24)</f>
+        <f t="shared" si="4"/>
         <v>3.0664799999999999</v>
       </c>
       <c r="G24" s="4">
@@ -2003,7 +1999,7 @@
         <v>10.116</v>
       </c>
       <c r="J24" s="2">
-        <f>SLOPE(I20:I24,A20:A24)</f>
+        <f t="shared" si="5"/>
         <v>0.96432000000000007</v>
       </c>
       <c r="K24" s="4">
@@ -2017,7 +2013,7 @@
         <v>10.02</v>
       </c>
       <c r="N24" s="4">
-        <f>SLOPE(M20:M24,A20:A24)</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="O24" s="4">
@@ -2031,7 +2027,7 @@
         <v>0.50080000000000002</v>
       </c>
       <c r="R24" s="4">
-        <f>SLOPE(Q20:Q24,A20:A24)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
